--- a/artfynd/A 54843-2021 artfynd.xlsx
+++ b/artfynd/A 54843-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54843-2021 artfynd.xlsx
+++ b/artfynd/A 54843-2021 artfynd.xlsx
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>

--- a/artfynd/A 54843-2021 artfynd.xlsx
+++ b/artfynd/A 54843-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>97068424</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585887.5553718398</v>
+        <v>585888</v>
       </c>
       <c r="R2" t="n">
-        <v>7164048.626106997</v>
+        <v>7164049</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97068388</v>
+        <v>97068425</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586367.8554428269</v>
+        <v>586564</v>
       </c>
       <c r="R3" t="n">
-        <v>7163939.76723852</v>
+        <v>7163871</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97068480</v>
+        <v>97068426</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587033.4573218874</v>
+        <v>586802</v>
       </c>
       <c r="R4" t="n">
-        <v>7163793.303949868</v>
+        <v>7163805</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97068476</v>
+        <v>97068394</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586707.9931898204</v>
+        <v>585878</v>
       </c>
       <c r="R5" t="n">
-        <v>7163842.874442593</v>
+        <v>7164044</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97068399</v>
+        <v>97068395</v>
       </c>
       <c r="B6" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587024.9946491343</v>
+        <v>586565</v>
       </c>
       <c r="R6" t="n">
-        <v>7163758.246459238</v>
+        <v>7163870</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97068464</v>
+        <v>97068488</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585997.0594122751</v>
+        <v>586381</v>
       </c>
       <c r="R7" t="n">
-        <v>7164010.898315527</v>
+        <v>7163937</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97068386</v>
+        <v>97068432</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1506</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586610.9171547048</v>
+        <v>586064</v>
       </c>
       <c r="R8" t="n">
-        <v>7163866.750930146</v>
+        <v>7163988</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1325,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,54 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97068411</v>
+        <v>97068392</v>
       </c>
       <c r="B9" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586753.9032777692</v>
+        <v>586565</v>
       </c>
       <c r="R9" t="n">
-        <v>7163847.624440772</v>
+        <v>7163869</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1536,29 +1422,34 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1575,37 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97068391</v>
+        <v>97068445</v>
       </c>
       <c r="B10" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>2063</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587033.4573218874</v>
+        <v>586496</v>
       </c>
       <c r="R10" t="n">
-        <v>7163793.303949868</v>
+        <v>7163881</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1648,21 +1534,11 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1671,6 +1547,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1687,37 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97068449</v>
+        <v>97068446</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585846.1120721282</v>
+        <v>586368</v>
       </c>
       <c r="R11" t="n">
-        <v>7164022.957141315</v>
+        <v>7163927</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1760,21 +1646,11 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1783,6 +1659,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1799,37 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97068488</v>
+        <v>97068476</v>
       </c>
       <c r="B12" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586380.8522918141</v>
+        <v>586708</v>
       </c>
       <c r="R12" t="n">
-        <v>7163936.698750183</v>
+        <v>7163843</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1872,19 +1758,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,37 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97068470</v>
+        <v>97068477</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586798.5471267087</v>
+        <v>586384</v>
       </c>
       <c r="R13" t="n">
-        <v>7163806.349908798</v>
+        <v>7163938</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1984,19 +1855,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,37 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97068469</v>
+        <v>97068478</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586786.9364955908</v>
+        <v>586368</v>
       </c>
       <c r="R14" t="n">
-        <v>7163760.88789579</v>
+        <v>7163939</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2096,19 +1952,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,37 +1981,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97068453</v>
+        <v>97068479</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586742.4895377087</v>
+        <v>586027</v>
       </c>
       <c r="R15" t="n">
-        <v>7163825.378375514</v>
+        <v>7164007</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2208,19 +2049,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,19 +2078,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97068478</v>
+        <v>97068486</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2287,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586367.8798779232</v>
+        <v>586818</v>
       </c>
       <c r="R16" t="n">
-        <v>7163938.908364559</v>
+        <v>7163772</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2320,19 +2146,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,37 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97068393</v>
+        <v>97068487</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586990.8157567015</v>
+        <v>586801</v>
       </c>
       <c r="R17" t="n">
-        <v>7163764.573791513</v>
+        <v>7163840</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2432,19 +2243,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,15 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97068486</v>
+        <v>97068386</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,21 +2283,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586818.0191389661</v>
+        <v>586611</v>
       </c>
       <c r="R18" t="n">
-        <v>7163772.521909264</v>
+        <v>7163867</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2544,19 +2340,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,15 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97068410</v>
+        <v>97068388</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,39 +2380,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586849.015549807</v>
+        <v>586368</v>
       </c>
       <c r="R19" t="n">
-        <v>7163757.075545986</v>
+        <v>7163940</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2661,19 +2437,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,37 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97068446</v>
+        <v>97068389</v>
       </c>
       <c r="B20" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2063</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586368.2219698315</v>
+        <v>586486</v>
       </c>
       <c r="R20" t="n">
-        <v>7163926.884103619</v>
+        <v>7163890</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2773,21 +2534,11 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2796,21 +2547,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2827,37 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97068392</v>
+        <v>97068390</v>
       </c>
       <c r="B21" t="n">
-        <v>89732</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586564.7990379067</v>
+        <v>586158</v>
       </c>
       <c r="R21" t="n">
-        <v>7163869.303728261</v>
+        <v>7164027</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2900,44 +2631,19 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2954,37 +2660,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97068425</v>
+        <v>97068417</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2994,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586563.8778518556</v>
+        <v>586123</v>
       </c>
       <c r="R22" t="n">
-        <v>7163871.426441767</v>
+        <v>7164007</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3027,19 +2728,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,50 +2757,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97068463</v>
+        <v>97068415</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585946.0445597945</v>
+        <v>586284</v>
       </c>
       <c r="R23" t="n">
-        <v>7164019.33826819</v>
+        <v>7163948</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3139,19 +2830,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,50 +2859,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97068445</v>
+        <v>97068416</v>
       </c>
       <c r="B24" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586495.5984496771</v>
+        <v>586835</v>
       </c>
       <c r="R24" t="n">
-        <v>7163881.514548127</v>
+        <v>7163781</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3251,21 +2932,11 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3274,21 +2945,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3305,15 +2961,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97068407</v>
+        <v>97068403</v>
       </c>
       <c r="B25" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586912.8021855149</v>
+        <v>586300</v>
       </c>
       <c r="R25" t="n">
-        <v>7163768.786657063</v>
+        <v>7163935</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3383,19 +3034,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,15 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97068473</v>
+        <v>97068409</v>
       </c>
       <c r="B26" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3438,34 +3074,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586769.7393905055</v>
+        <v>586874</v>
       </c>
       <c r="R26" t="n">
-        <v>7163865.69881043</v>
+        <v>7163741</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3495,19 +3136,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3534,15 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97068465</v>
+        <v>97068410</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3550,34 +3176,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586863.2422838958</v>
+        <v>586849</v>
       </c>
       <c r="R27" t="n">
-        <v>7163756.193112512</v>
+        <v>7163757</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3607,19 +3238,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,15 +3267,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97068485</v>
+        <v>97068411</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3662,34 +3278,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587066.1580403879</v>
+        <v>586754</v>
       </c>
       <c r="R28" t="n">
-        <v>7163838.511822295</v>
+        <v>7163847</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3719,19 +3339,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,15 +3368,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97068452</v>
+        <v>97068412</v>
       </c>
       <c r="B29" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3774,34 +3379,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586491.2532320247</v>
+        <v>585895</v>
       </c>
       <c r="R29" t="n">
-        <v>7163913.195327892</v>
+        <v>7164016</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3831,19 +3440,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,37 +3469,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97068428</v>
+        <v>97068393</v>
       </c>
       <c r="B30" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3910,10 +3504,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587033.4573218874</v>
+        <v>586991</v>
       </c>
       <c r="R30" t="n">
-        <v>7163793.303949868</v>
+        <v>7163765</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3943,19 +3537,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,15 +3566,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97068412</v>
+        <v>97068490</v>
       </c>
       <c r="B31" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3998,38 +3577,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585894.9402821963</v>
+        <v>587104</v>
       </c>
       <c r="R31" t="n">
-        <v>7164015.742980422</v>
+        <v>7163812</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4059,19 +3634,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4098,37 +3663,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>97068456</v>
+        <v>97068399</v>
       </c>
       <c r="B32" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4138,10 +3698,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586753.9032777692</v>
+        <v>587025</v>
       </c>
       <c r="R32" t="n">
-        <v>7163847.624440772</v>
+        <v>7163758</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4171,19 +3731,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,19 +3760,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>97068483</v>
+        <v>97068480</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4250,10 +3795,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587080.4349183182</v>
+        <v>587034</v>
       </c>
       <c r="R33" t="n">
-        <v>7163820.869433368</v>
+        <v>7163793</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4283,19 +3828,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,19 +3857,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>97068484</v>
+        <v>97068481</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4362,10 +3892,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587082.017039254</v>
+        <v>587042</v>
       </c>
       <c r="R34" t="n">
-        <v>7163855.729037888</v>
+        <v>7163786</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4395,19 +3925,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,37 +3954,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>97068450</v>
+        <v>97068482</v>
       </c>
       <c r="B35" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4474,10 +3989,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586491.2305101525</v>
+        <v>587070</v>
       </c>
       <c r="R35" t="n">
-        <v>7163929.096845469</v>
+        <v>7163832</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4507,19 +4022,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,37 +4051,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>97068490</v>
+        <v>97068483</v>
       </c>
       <c r="B36" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4586,10 +4086,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587104.3552936856</v>
+        <v>587080</v>
       </c>
       <c r="R36" t="n">
-        <v>7163812.099861154</v>
+        <v>7163821</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4619,19 +4119,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4658,37 +4148,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>97068467</v>
+        <v>97068484</v>
       </c>
       <c r="B37" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4698,10 +4183,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586834.9977916798</v>
+        <v>587082</v>
       </c>
       <c r="R37" t="n">
-        <v>7163780.744096618</v>
+        <v>7163856</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4731,19 +4216,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4770,19 +4245,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>97068482</v>
+        <v>97068485</v>
       </c>
       <c r="B38" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4810,10 +4280,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587070.2249723045</v>
+        <v>587066</v>
       </c>
       <c r="R38" t="n">
-        <v>7163831.751571486</v>
+        <v>7163839</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4843,19 +4313,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,15 +4342,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>97068454</v>
+        <v>97068391</v>
       </c>
       <c r="B39" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4898,21 +4353,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4922,10 +4377,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586717.9073520437</v>
+        <v>587034</v>
       </c>
       <c r="R39" t="n">
-        <v>7163842.298015191</v>
+        <v>7163793</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4955,19 +4410,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,37 +4439,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>97068432</v>
+        <v>97068418</v>
       </c>
       <c r="B40" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5034,10 +4474,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586064.4092325612</v>
+        <v>586921</v>
       </c>
       <c r="R40" t="n">
-        <v>7163987.880156316</v>
+        <v>7163773</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5067,19 +4507,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5106,15 +4536,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>97068403</v>
+        <v>97068400</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5151,10 +4576,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586300.0056502451</v>
+        <v>587014</v>
       </c>
       <c r="R41" t="n">
-        <v>7163934.829169592</v>
+        <v>7163780</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5184,19 +4609,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5223,15 +4638,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>97068472</v>
+        <v>97068402</v>
       </c>
       <c r="B42" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5239,34 +4649,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586752.0974420788</v>
+        <v>586991</v>
       </c>
       <c r="R42" t="n">
-        <v>7163850.581442491</v>
+        <v>7163765</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5296,19 +4711,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5335,15 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>97068479</v>
+        <v>97068404</v>
       </c>
       <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5351,34 +4751,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586027.2782617215</v>
+        <v>587081</v>
       </c>
       <c r="R43" t="n">
-        <v>7164007.456814759</v>
+        <v>7163822</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5408,19 +4813,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5447,15 +4842,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>97068477</v>
+        <v>97068405</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5463,34 +4853,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586383.8254242204</v>
+        <v>587063</v>
       </c>
       <c r="R44" t="n">
-        <v>7163938.07270529</v>
+        <v>7163842</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5520,19 +4915,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5559,15 +4944,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>97068461</v>
+        <v>97068406</v>
       </c>
       <c r="B45" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5575,34 +4955,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586283.7183665913</v>
+        <v>587206</v>
       </c>
       <c r="R45" t="n">
-        <v>7163947.689493527</v>
+        <v>7163797</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5632,19 +5017,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5671,15 +5046,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>97068468</v>
+        <v>97068407</v>
       </c>
       <c r="B46" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5687,34 +5057,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586804.4321184139</v>
+        <v>586913</v>
       </c>
       <c r="R46" t="n">
-        <v>7163826.289236728</v>
+        <v>7163769</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5744,19 +5119,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5783,55 +5148,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>97068402</v>
+        <v>97068428</v>
       </c>
       <c r="B47" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vojmån, Forsnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586990.8157567015</v>
+        <v>587034</v>
       </c>
       <c r="R47" t="n">
-        <v>7163764.573791513</v>
+        <v>7163793</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5861,19 +5216,9 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5897,2729 +5242,6 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>97068405</v>
-      </c>
-      <c r="B48" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>587063.0619360923</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7163841.43166457</v>
-      </c>
-      <c r="S48" t="n">
-        <v>25</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>97068457</v>
-      </c>
-      <c r="B49" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>586495.5984496771</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7163881.514548127</v>
-      </c>
-      <c r="S49" t="n">
-        <v>25</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>97068406</v>
-      </c>
-      <c r="B50" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>587205.4783544488</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7163797.380648516</v>
-      </c>
-      <c r="S50" t="n">
-        <v>25</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>97068415</v>
-      </c>
-      <c r="B51" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>586283.7183665913</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7163947.689493527</v>
-      </c>
-      <c r="S51" t="n">
-        <v>25</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>97068390</v>
-      </c>
-      <c r="B52" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>586157.9650212923</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7164027.064673957</v>
-      </c>
-      <c r="S52" t="n">
-        <v>25</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>97068417</v>
-      </c>
-      <c r="B53" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>586123.2323890944</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7164007.59891751</v>
-      </c>
-      <c r="S53" t="n">
-        <v>25</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>97068448</v>
-      </c>
-      <c r="B54" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>587024.9700284512</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7163759.105385375</v>
-      </c>
-      <c r="S54" t="n">
-        <v>25</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>97068389</v>
-      </c>
-      <c r="B55" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>586485.4520338529</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7163890.251134682</v>
-      </c>
-      <c r="S55" t="n">
-        <v>25</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>97068426</v>
-      </c>
-      <c r="B56" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>658</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>586801.5938867836</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7163805.147596772</v>
-      </c>
-      <c r="S56" t="n">
-        <v>25</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>97068409</v>
-      </c>
-      <c r="B57" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>586874.4345944324</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7163741.039983371</v>
-      </c>
-      <c r="S57" t="n">
-        <v>25</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>97068447</v>
-      </c>
-      <c r="B58" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>586948.6014397563</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7163796.030239192</v>
-      </c>
-      <c r="S58" t="n">
-        <v>25</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>97068466</v>
-      </c>
-      <c r="B59" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>586850.28096695</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7163757.971374483</v>
-      </c>
-      <c r="S59" t="n">
-        <v>25</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>97068487</v>
-      </c>
-      <c r="B60" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>586801.0170154111</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7163840.375104251</v>
-      </c>
-      <c r="S60" t="n">
-        <v>25</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>97068481</v>
-      </c>
-      <c r="B61" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>587041.8610960036</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7163785.37845499</v>
-      </c>
-      <c r="S61" t="n">
-        <v>25</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>97068394</v>
-      </c>
-      <c r="B62" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>585877.7757650651</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7164044.481540397</v>
-      </c>
-      <c r="S62" t="n">
-        <v>25</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>97068418</v>
-      </c>
-      <c r="B63" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>586920.861420747</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7163772.88570429</v>
-      </c>
-      <c r="S63" t="n">
-        <v>25</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>97068416</v>
-      </c>
-      <c r="B64" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>586834.9977916798</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7163780.744096618</v>
-      </c>
-      <c r="S64" t="n">
-        <v>25</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>97068458</v>
-      </c>
-      <c r="B65" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>586551.6057938823</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7163879.242652002</v>
-      </c>
-      <c r="S65" t="n">
-        <v>25</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>97068404</v>
-      </c>
-      <c r="B66" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>587081.2702562093</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7163821.75300911</v>
-      </c>
-      <c r="S66" t="n">
-        <v>25</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>97068462</v>
-      </c>
-      <c r="B67" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>586167.0550695998</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7164025.17382891</v>
-      </c>
-      <c r="S67" t="n">
-        <v>25</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>97068400</v>
-      </c>
-      <c r="B68" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>587013.6169972874</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7163779.840880235</v>
-      </c>
-      <c r="S68" t="n">
-        <v>25</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>97068395</v>
-      </c>
-      <c r="B69" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>586564.7745472231</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7163870.162622222</v>
-      </c>
-      <c r="S69" t="n">
-        <v>25</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>97068459</v>
-      </c>
-      <c r="B70" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>586369.0819131173</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7163926.908569237</v>
-      </c>
-      <c r="S70" t="n">
-        <v>25</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>97068460</v>
-      </c>
-      <c r="B71" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Vojmån, Forsnäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>586285.651261291</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7163970.52282741</v>
-      </c>
-      <c r="S71" t="n">
-        <v>25</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2021-11-02</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
